--- a/output/pdf_financials_xlsx/EBCD.P.xlsx
+++ b/output/pdf_financials_xlsx/EBCD.P.xlsx
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00735</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.017309</v>
       </c>
     </row>
     <row r="13">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.344721</v>
+        <v>-0.352071</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.047957</v>
+        <v>-0.065266</v>
       </c>
     </row>
     <row r="28">
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.344721</v>
+        <v>-0.352071</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.047957</v>
+        <v>-0.065266</v>
       </c>
     </row>
     <row r="30">
@@ -1185,16 +1185,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.09821299999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.546853</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.140132</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.010692</v>
       </c>
     </row>
     <row r="35">
@@ -1223,16 +1223,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.09821299999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.546853</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.140132</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.010692</v>
       </c>
     </row>
     <row r="37">
@@ -1451,16 +1451,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.108213</v>
+        <v>0.01</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.546853</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.140132</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.013643</v>
+        <v>0.002951</v>
       </c>
     </row>
     <row r="49">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">

--- a/output/pdf_financials_xlsx/EBCD.P.xlsx
+++ b/output/pdf_financials_xlsx/EBCD.P.xlsx
@@ -513,15 +513,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -563,15 +559,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.000184</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.002947</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.000692</v>
@@ -586,15 +578,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -609,15 +597,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.002245</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -632,15 +616,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.042196</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.138459</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.352071</v>
@@ -660,10 +640,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="3" t="n">
+        <v>-0.138459</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-0.352071</v>
@@ -678,15 +656,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.00735</v>
@@ -701,15 +675,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -724,15 +694,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -747,15 +713,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -770,15 +732,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.042196</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.138459</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.344721</v>
@@ -793,15 +751,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -870,15 +824,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.042196</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.138459</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.344721</v>
@@ -893,15 +843,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -916,15 +862,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -942,10 +884,8 @@
       <c r="B23" s="3" t="n">
         <v>-0.042196</v>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C23" s="3" t="n">
+        <v>-0.138459</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.344721</v>
@@ -960,15 +900,11 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>-0.04</v>
@@ -983,15 +919,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>-0.04</v>
@@ -1006,15 +938,11 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>1.0549</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>6.92295</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>8.618024999999999</v>
@@ -1031,15 +959,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.042196</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.138459</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.352071</v>
@@ -1054,15 +978,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -1077,15 +997,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.042196</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.138459</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.352071</v>
@@ -1127,15 +1043,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -3271,7 +3183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6200,10 +6112,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F79" s="5" t="n">
+        <v>0.002245</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -6235,15 +6145,11 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E80" s="5" t="n">
+        <v>0.000184</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0.001447</v>
       </c>
       <c r="G80" s="5" t="n">
         <v>0.000692</v>
@@ -6273,15 +6179,11 @@
           <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E81" s="5" t="n">
+        <v>0.042012</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0.08094700000000001</v>
       </c>
       <c r="G81" s="5" t="n">
         <v>0.351379</v>
@@ -6311,15 +6213,11 @@
           <t>OperatingExpense</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E82" s="5" t="n">
+        <v>0.042196</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0.138459</v>
       </c>
       <c r="G82" s="5" t="n">
         <v>0.352071</v>
@@ -6354,10 +6252,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F83" s="5" t="n">
+        <v>-0.138459</v>
       </c>
       <c r="G83" s="5" t="n">
         <v>-0.352071</v>
@@ -6425,15 +6321,11 @@
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E85" s="5" t="n">
+        <v>-0.042196</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>-0.138459</v>
       </c>
       <c r="G85" s="5" t="n">
         <v>-0.344721</v>
@@ -6463,10 +6355,8 @@
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E86" s="5" t="n">
+        <v>-4e-08</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6497,21 +6387,207 @@
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E87" s="5" t="n">
+        <v>1.007385</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>8.600822000000001</v>
       </c>
       <c r="G87" s="5" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H87" s="5" t="n">
         <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>REVENUE $</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Stock-based compensation (Note 5)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.05232</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>NET LOSS PER SHARE - BASIC AND DILUTED (Note 4) $</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Bank charges</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>0.000184</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>
